--- a/outputs/daily/hr_rankings_2026-09-20_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-20_remaining.xlsx
@@ -12423,27 +12423,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>682674</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Victor Bericoto</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12453,14 +12453,26 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Jack Perkins</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>678022</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L45" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12478,22 +12490,22 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>53.5</v>
+        <v>52.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="R45" t="n">
         <v>27.6</v>
       </c>
       <c r="S45" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T45" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U45" t="n">
-        <v>37.8</v>
+        <v>65.2</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -12507,7 +12519,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -12532,7 +12544,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -12549,110 +12561,134 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/16, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.65</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>100.3441</t>
+          <t>102.9391</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.4741</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.2155</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.3384</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.39</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>72.04</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.173</t>
-        </is>
-      </c>
-      <c r="BA45" t="inlineStr"/>
-      <c r="BB45" t="inlineStr"/>
-      <c r="BC45" t="inlineStr"/>
-      <c r="BD45" t="inlineStr"/>
-      <c r="BE45" t="inlineStr"/>
-      <c r="BF45" t="inlineStr"/>
+          <t>0.1881</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>9.18</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>36.86</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>87.94</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>0.3769</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>0.1503</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>33.12</t>
+        </is>
+      </c>
       <c r="BG45" t="inlineStr"/>
       <c r="BH45" t="inlineStr"/>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -12663,27 +12699,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>682674</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Victor Bericoto</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12693,24 +12729,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Jack Perkins</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>678022</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>51.8</v>
       </c>
@@ -12730,22 +12754,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>52.7</v>
+        <v>53.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="R46" t="n">
         <v>27.6</v>
       </c>
       <c r="S46" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T46" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U46" t="n">
-        <v>65.2</v>
+        <v>35.6</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -12759,7 +12783,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -12784,7 +12808,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
@@ -12801,134 +12825,110 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/17, 1 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>90.65</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>102.9391</t>
+          <t>100.3441</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.4741</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.2155</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.3384</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>77.39</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>72.04</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.1881</t>
-        </is>
-      </c>
-      <c r="BA46" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
-      </c>
-      <c r="BB46" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
-      </c>
-      <c r="BC46" t="inlineStr">
-        <is>
-          <t>87.94</t>
-        </is>
-      </c>
-      <c r="BD46" t="inlineStr">
-        <is>
-          <t>0.3769</t>
-        </is>
-      </c>
-      <c r="BE46" t="inlineStr">
-        <is>
-          <t>0.1503</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
+          <t>0.173</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr"/>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -31863,27 +31863,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>667472</t>
+          <t>668904</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:07:00Z</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -31893,14 +31893,26 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Ryan Johnson</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>696270</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L117" t="n">
-        <v>43.5</v>
+        <v>43.7</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -31914,26 +31926,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>26</v>
+        <v>40.4</v>
       </c>
       <c r="Q117" t="n">
-        <v>41.2</v>
+        <v>46.1</v>
       </c>
       <c r="R117" t="n">
-        <v>39.3</v>
+        <v>28.2</v>
       </c>
       <c r="S117" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T117" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U117" t="n">
-        <v>25.3</v>
+        <v>10.8</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -31947,7 +31959,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -31972,7 +31984,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr"/>
@@ -31989,110 +32001,134 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>99.1984</t>
+          <t>100.593</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.3099</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>71.04</t>
+          <t>74.65</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>46.51</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1078</t>
-        </is>
-      </c>
-      <c r="BA117" t="inlineStr"/>
-      <c r="BB117" t="inlineStr"/>
-      <c r="BC117" t="inlineStr"/>
-      <c r="BD117" t="inlineStr"/>
-      <c r="BE117" t="inlineStr"/>
-      <c r="BF117" t="inlineStr"/>
+          <t>0.1531</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>9.48</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>36.42</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>87.68</t>
+        </is>
+      </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>0.4332</t>
+        </is>
+      </c>
+      <c r="BE117" t="inlineStr">
+        <is>
+          <t>0.1833</t>
+        </is>
+      </c>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>34.09</t>
+        </is>
+      </c>
       <c r="BG117" t="inlineStr"/>
       <c r="BH117" t="inlineStr"/>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -32103,22 +32139,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>667472</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -32133,24 +32169,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Patrick Sandoval</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>663776</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
         <v>43.5</v>
       </c>
@@ -32166,26 +32190,26 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>44.4</v>
+        <v>26</v>
       </c>
       <c r="Q118" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R118" t="n">
-        <v>27.6</v>
+        <v>39.3</v>
       </c>
       <c r="S118" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T118" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U118" t="n">
-        <v>39.5</v>
+        <v>25.3</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -32199,7 +32223,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -32224,7 +32248,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr"/>
@@ -32241,12 +32265,12 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -32256,12 +32280,12 @@
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 6.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -32271,104 +32295,80 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>100.1512</t>
+          <t>99.1984</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.4395</t>
+          <t>0.3677</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.1942</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0.3099</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>73.72</t>
+          <t>71.04</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.2176</t>
-        </is>
-      </c>
-      <c r="BA118" t="inlineStr">
-        <is>
-          <t>6.9</t>
-        </is>
-      </c>
-      <c r="BB118" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
-      <c r="BC118" t="inlineStr">
-        <is>
-          <t>87.8</t>
-        </is>
-      </c>
-      <c r="BD118" t="inlineStr">
-        <is>
-          <t>0.442</t>
-        </is>
-      </c>
-      <c r="BE118" t="inlineStr">
-        <is>
-          <t>0.163</t>
-        </is>
-      </c>
-      <c r="BF118" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
+          <t>0.1078</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr"/>
+      <c r="BB118" t="inlineStr"/>
+      <c r="BC118" t="inlineStr"/>
+      <c r="BD118" t="inlineStr"/>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr"/>
       <c r="BG118" t="inlineStr"/>
       <c r="BH118" t="inlineStr"/>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -32379,27 +32379,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brett Callahan</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -32409,22 +32409,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>663776</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -32442,26 +32442,26 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>43.3</v>
+        <v>44.4</v>
       </c>
       <c r="Q119" t="n">
-        <v>44.8</v>
+        <v>34.3</v>
       </c>
       <c r="R119" t="n">
         <v>27.6</v>
       </c>
       <c r="S119" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T119" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U119" t="n">
-        <v>7</v>
+        <v>39.5</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -32500,7 +32500,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -32517,134 +32517,134 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/12, 0 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.77</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>100.7322</t>
+          <t>100.1512</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>0.4395</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
+          <t>0.1942</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
+          <t>0.334</t>
+        </is>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>73.72</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>32.74</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>40.52</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>34.54</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>0.2176</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>87.8</t>
+        </is>
+      </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>0.442</t>
+        </is>
+      </c>
+      <c r="BE119" t="inlineStr">
+        <is>
           <t>0.163</t>
         </is>
       </c>
-      <c r="AT119" t="inlineStr">
-        <is>
-          <t>0.297</t>
-        </is>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>74.6</t>
-        </is>
-      </c>
-      <c r="AV119" t="inlineStr">
-        <is>
-          <t>46.7</t>
-        </is>
-      </c>
-      <c r="AW119" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>0.143</t>
-        </is>
-      </c>
-      <c r="BA119" t="inlineStr">
-        <is>
-          <t>7.42</t>
-        </is>
-      </c>
-      <c r="BB119" t="inlineStr">
-        <is>
-          <t>44.67</t>
-        </is>
-      </c>
-      <c r="BC119" t="inlineStr">
-        <is>
-          <t>90.42</t>
-        </is>
-      </c>
-      <c r="BD119" t="inlineStr">
-        <is>
-          <t>0.4293</t>
-        </is>
-      </c>
-      <c r="BE119" t="inlineStr">
-        <is>
-          <t>0.1573</t>
-        </is>
-      </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr"/>
       <c r="BH119" t="inlineStr"/>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -32655,27 +32655,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>668904</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Brett Callahan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-20T20:07:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -32685,17 +32685,17 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -32718,26 +32718,26 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>40.4</v>
+        <v>43.3</v>
       </c>
       <c r="Q120" t="n">
-        <v>46.1</v>
+        <v>44.8</v>
       </c>
       <c r="R120" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S120" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T120" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U120" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -32776,7 +32776,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr"/>
@@ -32793,12 +32793,12 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -32808,119 +32808,119 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 2/12, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>100.593</t>
+          <t>100.7322</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.3979</t>
+          <t>0.377</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.297</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>74.65</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>49.82</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.1531</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.4293</t>
         </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
-          <t>0.1833</t>
+          <t>0.1573</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="BG120" t="inlineStr"/>
       <c r="BH120" t="inlineStr"/>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr"/>
@@ -36074,7 +36074,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -39483,24 +39483,24 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>605170</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>2026-09-20T20:07:00Z</t>
@@ -39513,17 +39513,17 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -39546,26 +39546,26 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>11.5</v>
+        <v>29.6</v>
       </c>
       <c r="Q145" t="n">
-        <v>47.7</v>
+        <v>44.6</v>
       </c>
       <c r="R145" t="n">
         <v>28.2</v>
       </c>
       <c r="S145" t="n">
-        <v>92.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T145" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U145" t="n">
-        <v>25.8</v>
+        <v>19.5</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -39604,7 +39604,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr"/>
@@ -39621,12 +39621,12 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
@@ -39636,12 +39636,12 @@
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 18.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -39651,97 +39651,97 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>96.6684</t>
+          <t>98.9527</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.3844</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.1476</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.1107</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>87.96</t>
+          <t>87.68</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.4419</t>
+          <t>0.4332</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.1987</t>
+          <t>0.1833</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>34.09</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr"/>
@@ -39759,27 +39759,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>682663</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Agustin Ramirez</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T20:07:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -39789,17 +39789,17 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -39822,26 +39822,26 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>31</v>
+        <v>11.5</v>
       </c>
       <c r="Q146" t="n">
-        <v>43</v>
+        <v>47.7</v>
       </c>
       <c r="R146" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S146" t="n">
-        <v>59.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T146" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U146" t="n">
-        <v>78.7</v>
+        <v>25.8</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -39880,7 +39880,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr"/>
@@ -39897,134 +39897,134 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 18.5 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>102.6626</t>
+          <t>96.6684</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.1266</t>
+          <t>0.094</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.2998</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>75.62</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.1463</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.4419</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1987</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr"/>
       <c r="BH146" t="inlineStr"/>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -40311,27 +40311,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>682877</t>
+          <t>682663</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Juan Brito</t>
+          <t>Agustin Ramirez</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -40341,14 +40341,26 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Walker Buehler</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>621111</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L148" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -40362,26 +40374,26 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>16.6</v>
+        <v>31</v>
       </c>
       <c r="Q148" t="n">
-        <v>40.2</v>
+        <v>43</v>
       </c>
       <c r="R148" t="n">
-        <v>39.3</v>
+        <v>22.6</v>
       </c>
       <c r="S148" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T148" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U148" t="n">
-        <v>54.3</v>
+        <v>75.8</v>
       </c>
       <c r="V148" t="inlineStr">
         <is>
@@ -40395,7 +40407,7 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
@@ -40420,7 +40432,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr"/>
@@ -40437,27 +40449,27 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
@@ -40467,80 +40479,104 @@
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>96.9148</t>
+          <t>102.6626</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1266</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>0.2998</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>75.62</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>0.138</t>
-        </is>
-      </c>
-      <c r="BA148" t="inlineStr"/>
-      <c r="BB148" t="inlineStr"/>
-      <c r="BC148" t="inlineStr"/>
-      <c r="BD148" t="inlineStr"/>
-      <c r="BE148" t="inlineStr"/>
-      <c r="BF148" t="inlineStr"/>
+          <t>0.1463</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>8.59</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>38.15</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>88.88</t>
+        </is>
+      </c>
+      <c r="BD148" t="inlineStr">
+        <is>
+          <t>0.4171</t>
+        </is>
+      </c>
+      <c r="BE148" t="inlineStr">
+        <is>
+          <t>0.1645</t>
+        </is>
+      </c>
+      <c r="BF148" t="inlineStr">
+        <is>
+          <t>23.44</t>
+        </is>
+      </c>
       <c r="BG148" t="inlineStr"/>
       <c r="BH148" t="inlineStr"/>
       <c r="BI148" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ148" t="inlineStr"/>
@@ -40551,22 +40587,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>682877</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Juan Brito</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -40581,24 +40617,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Jack Perkins</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>678022</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="n">
         <v>40.5</v>
       </c>
@@ -40614,26 +40638,26 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P149" t="n">
-        <v>21.6</v>
+        <v>16.6</v>
       </c>
       <c r="Q149" t="n">
-        <v>41</v>
+        <v>40.2</v>
       </c>
       <c r="R149" t="n">
-        <v>27.6</v>
+        <v>39.3</v>
       </c>
       <c r="S149" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T149" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U149" t="n">
-        <v>75.90000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="V149" t="inlineStr">
         <is>
@@ -40647,7 +40671,7 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -40672,7 +40696,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr"/>
@@ -40689,67 +40713,67 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>98.4634</t>
+          <t>96.9148</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>0.285</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr">
@@ -40759,64 +40783,40 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>0.164</t>
-        </is>
-      </c>
-      <c r="BA149" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
-      </c>
-      <c r="BB149" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
-      </c>
-      <c r="BC149" t="inlineStr">
-        <is>
-          <t>87.94</t>
-        </is>
-      </c>
-      <c r="BD149" t="inlineStr">
-        <is>
-          <t>0.3769</t>
-        </is>
-      </c>
-      <c r="BE149" t="inlineStr">
-        <is>
-          <t>0.1503</t>
-        </is>
-      </c>
-      <c r="BF149" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
+          <t>0.138</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr"/>
+      <c r="BB149" t="inlineStr"/>
+      <c r="BC149" t="inlineStr"/>
+      <c r="BD149" t="inlineStr"/>
+      <c r="BE149" t="inlineStr"/>
+      <c r="BF149" t="inlineStr"/>
       <c r="BG149" t="inlineStr"/>
       <c r="BH149" t="inlineStr"/>
       <c r="BI149" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ149" t="inlineStr"/>
@@ -40827,22 +40827,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>596115</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Trevor Story</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -40857,17 +40857,17 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Jack Perkins</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>678022</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -40890,26 +40890,26 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>26.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q150" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R150" t="n">
         <v>27.6</v>
       </c>
       <c r="S150" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T150" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U150" t="n">
-        <v>54.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
@@ -40948,7 +40948,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr"/>
@@ -40965,134 +40965,134 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>88.53</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>99.7938</t>
+          <t>98.4634</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>0.3559</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>0.1275</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.2711</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>71.03</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>0.1294</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>36.86</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>87.94</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>0.1534</t>
+          <t>0.1503</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr"/>
       <c r="BH150" t="inlineStr"/>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr"/>
@@ -41103,27 +41103,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>596115</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Trevor Story</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -41138,17 +41138,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -41170,10 +41170,10 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>35.9</v>
+        <v>26.5</v>
       </c>
       <c r="Q151" t="n">
-        <v>37.7</v>
+        <v>43</v>
       </c>
       <c r="R151" t="n">
         <v>27.6</v>
@@ -41185,7 +41185,7 @@
         <v>50</v>
       </c>
       <c r="U151" t="n">
-        <v>18.3</v>
+        <v>54.3</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
@@ -41241,12 +41241,12 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -41256,12 +41256,12 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 10.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -41271,104 +41271,104 @@
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.53</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>99.464</t>
+          <t>99.7938</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>0.3974</t>
+          <t>0.3559</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.1275</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>0.2969</t>
+          <t>0.2711</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>73.71</t>
+          <t>71.03</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.1294</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>88.06</t>
+          <t>88.99</t>
         </is>
       </c>
       <c r="BD151" t="inlineStr">
         <is>
-          <t>0.4213</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE151" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1534</t>
         </is>
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="BG151" t="inlineStr"/>
       <c r="BH151" t="inlineStr"/>
       <c r="BI151" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ151" t="inlineStr"/>
@@ -41379,27 +41379,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>605170</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Victor Caratini</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-20T20:07:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -41409,22 +41409,22 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -41442,26 +41442,26 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>29.6</v>
+        <v>35.9</v>
       </c>
       <c r="Q152" t="n">
-        <v>44.6</v>
+        <v>37.7</v>
       </c>
       <c r="R152" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S152" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T152" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U152" t="n">
-        <v>13.6</v>
+        <v>18.3</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -41517,134 +41517,134 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>98.9527</t>
+          <t>99.464</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.3844</t>
+          <t>0.3974</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.1476</t>
+          <t>0.1683</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2969</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>73.71</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>36.67</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.1107</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>37.16</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>88.06</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.4213</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>0.1833</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr"/>
       <c r="BH152" t="inlineStr"/>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -54973,7 +54973,7 @@
         <v>50</v>
       </c>
       <c r="U202" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V202" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
@@ -55044,7 +55044,7 @@
       </c>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 1 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL202" t="inlineStr">
